--- a/artfynd/A 12780-2026 artfynd.xlsx
+++ b/artfynd/A 12780-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155612</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131155616</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131155615</v>
       </c>
       <c r="B4" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131155809</v>
       </c>
       <c r="B5" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131155614</v>
       </c>
       <c r="B6" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131155613</v>
       </c>
       <c r="B7" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12780-2026 artfynd.xlsx
+++ b/artfynd/A 12780-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155612</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131155616</v>
       </c>
       <c r="B3" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131155615</v>
       </c>
       <c r="B4" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131155809</v>
       </c>
       <c r="B5" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131155614</v>
       </c>
       <c r="B6" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131155613</v>
       </c>
       <c r="B7" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12780-2026 artfynd.xlsx
+++ b/artfynd/A 12780-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131155612</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131155616</v>
+        <v>131155613</v>
       </c>
       <c r="B3" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574052</v>
+        <v>574031</v>
       </c>
       <c r="R3" t="n">
-        <v>6700025</v>
+        <v>6699961</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131155615</v>
+        <v>131155614</v>
       </c>
       <c r="B4" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574051</v>
+        <v>574036</v>
       </c>
       <c r="R4" t="n">
-        <v>6700017</v>
+        <v>6699976</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131155809</v>
+        <v>131155615</v>
       </c>
       <c r="B5" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,19 +1024,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1046,13 +1037,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574140</v>
+        <v>574051</v>
       </c>
       <c r="R5" t="n">
-        <v>6699988</v>
+        <v>6700017</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1073,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Uppskrämd. Såg ej individen, men tror tjäder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131155614</v>
+        <v>131155616</v>
       </c>
       <c r="B6" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,7 +1134,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1158,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574036</v>
+        <v>574052</v>
       </c>
       <c r="R6" t="n">
-        <v>6699976</v>
+        <v>6700025</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131155613</v>
+        <v>131155617</v>
       </c>
       <c r="B7" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,7 +1241,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1265,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574031</v>
+        <v>574064</v>
       </c>
       <c r="R7" t="n">
-        <v>6699961</v>
+        <v>6700068</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,6 +1310,234 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Fågelinventering Hålsberget 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131155618</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>N om Kalkgruvmossen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>574067</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6700082</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Albin Kozma</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fågelinventering Hålsberget 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131155809</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>N om Kalkgruvmossen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>574140</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6699988</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskrämd. Såg ej individen, men tror tjäder.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Albin Kozma</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>

--- a/artfynd/A 12780-2026 artfynd.xlsx
+++ b/artfynd/A 12780-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155612</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155613</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155615</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155616</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155617</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155618</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,8 +1582,23 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>